--- a/datos/directorio_forjar.xlsx
+++ b/datos/directorio_forjar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D22900-6AB3-4565-AF09-A46B3F166DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C37A85F-FE3A-4898-A8ED-0BAEF679935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,8 +81,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="169" formatCode="0.00000000000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -117,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -125,17 +125,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -453,82 +469,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>4.7377894857109597</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="4">
         <v>-74.091556748332394</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>4.5752065189313402</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>-74.151253557671495</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>4.57935554987393</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>-74.101570213492707</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/datos/directorio_forjar.xlsx
+++ b/datos/directorio_forjar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carol\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\Gestion de conocimiento\gestor-conocimiento-2025\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C37A85F-FE3A-4898-A8ED-0BAEF679935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC30506-4E51-414A-81B8-742C03E184F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,13 +67,13 @@
     <t>https://maps.app.goo.gl/W7w7Ck5WoxRwzpYx8</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/oAztqaBt9KPS97cn9</t>
-  </si>
-  <si>
     <t>Carrera 44 # 58 C - 90 Sur</t>
   </si>
   <si>
-    <t>Carrera 12G # 22B-29 Sur</t>
+    <t>Carrera 12G # 22B - 61 Sur</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Woccs9GMfvdKQrDs7</t>
   </si>
 </sst>
 </file>
@@ -516,7 +516,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3">
         <v>4.5752065189313402</v>
@@ -536,22 +536,21 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.5789965257665903</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-74.1019230983417</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4.57935554987393</v>
-      </c>
-      <c r="E4" s="3">
-        <v>-74.101570213492707</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" xr:uid="{69B84CFC-6E9A-4755-8326-97A389574060}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{87D5CA30-10A3-4A9F-87C4-D55E5AB722C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
